--- a/labs/lab-04-workbook-rules-and-personalisation/data/BrightPath_Client_Orders_Raw.xlsx
+++ b/labs/lab-04-workbook-rules-and-personalisation/data/BrightPath_Client_Orders_Raw.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="30" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
           <t>Region</t>
